--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>51427</v>
+        <v>51054</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>1776</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.04825235449422706</v>
+        <v>0.04090318004492257</v>
       </c>
       <c r="J56" t="n">
         <v>17244</v>
@@ -3024,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.7738285435031859</v>
+        <v>-0.7722316865417377</v>
       </c>
       <c r="J57" t="n">
         <v>4773</v>
@@ -6514,19 +6514,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>276898</v>
+        <v>276851</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-0.01075353330379982</v>
+        <v>-0.01092144561784586</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>243326</v>
+        <v>243237</v>
       </c>
       <c r="G56" t="n">
         <v>4444</v>
@@ -6535,7 +6535,7 @@
         <v>6053</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.3724836025241028</v>
+        <v>0.3720023575596014</v>
       </c>
       <c r="J56" t="n">
         <v>18362</v>
@@ -6557,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.2891064579736943</v>
+        <v>-0.288985772130135</v>
       </c>
       <c r="E57" t="n">
         <v>9</v>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.4640714198476891</v>
+        <v>-0.4638834369851892</v>
       </c>
       <c r="J57" t="n">
         <v>4167</v>
@@ -10089,7 +10089,7 @@
         <v>4082</v>
       </c>
       <c r="K56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -13610,19 +13610,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>260851</v>
+        <v>260842</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-0.0007010580997111487</v>
+        <v>-0.0007355363669100577</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>232603</v>
+        <v>231803</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -13631,13 +13631,13 @@
         <v>2645</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.3366895274243862</v>
+        <v>0.3321438920866171</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>28619</v>
       </c>
       <c r="K56" t="n">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57">
@@ -13653,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.07807138941387995</v>
+        <v>-0.07803957951556881</v>
       </c>
       <c r="E57" t="n">
         <v>9</v>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.8204745630143508</v>
+        <v>-0.8198619736572715</v>
       </c>
       <c r="J57" t="n">
         <v>12553</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>160451</v>
+        <v>160472</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-9.970897443087987e-05</v>
+        <v>3.115905450964996e-05</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.04722313977475989</v>
+        <v>-0.04734782391943766</v>
       </c>
       <c r="E57" t="n">
         <v>9</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -10074,7 +10074,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>36420</v>
+        <v>36323</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -10083,7 +10083,7 @@
         <v>18266</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.4835331777982746</v>
+        <v>0.4809017416309478</v>
       </c>
       <c r="J56" t="n">
         <v>4082</v>
@@ -10120,7 +10120,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.3416779431664411</v>
+        <v>-0.3405081609848138</v>
       </c>
       <c r="J57" t="n">
         <v>659</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2993,7 +2993,7 @@
         <v>17244</v>
       </c>
       <c r="K56" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
@@ -6538,10 +6538,10 @@
         <v>0.3720023575596014</v>
       </c>
       <c r="J56" t="n">
-        <v>18362</v>
+        <v>18370</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -10074,7 +10074,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>36323</v>
+        <v>36403</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -10083,7 +10083,7 @@
         <v>18266</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.4809017416309478</v>
+        <v>0.4830719982637947</v>
       </c>
       <c r="J56" t="n">
         <v>4082</v>
@@ -10120,7 +10120,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.3405081609848138</v>
+        <v>-0.341473229801167</v>
       </c>
       <c r="J57" t="n">
         <v>659</v>
@@ -13637,7 +13637,7 @@
         <v>28619</v>
       </c>
       <c r="K56" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2990,10 +2990,10 @@
         <v>0.04090318004492257</v>
       </c>
       <c r="J56" t="n">
-        <v>17244</v>
+        <v>17263</v>
       </c>
       <c r="K56" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57">
@@ -3234,7 +3234,7 @@
         <v>0.0238696833965009</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="n">
         <v>50754</v>
@@ -3530,7 +3530,7 @@
         <v>0.0238696833965009</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
         <v>50774</v>
@@ -6538,10 +6538,10 @@
         <v>0.3720023575596014</v>
       </c>
       <c r="J56" t="n">
-        <v>18370</v>
+        <v>18384</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -6782,7 +6782,7 @@
         <v>0.0460764752916209</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="n">
         <v>203510</v>
@@ -7078,7 +7078,7 @@
         <v>-0.003541315945887269</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
         <v>206373</v>
@@ -10330,7 +10330,7 @@
         <v>0.07276969945768424</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="n">
         <v>36862</v>
@@ -10626,7 +10626,7 @@
         <v>0.07276969945768424</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
         <v>36862</v>
@@ -13634,10 +13634,10 @@
         <v>0.3321438920866171</v>
       </c>
       <c r="J56" t="n">
-        <v>28619</v>
+        <v>28637</v>
       </c>
       <c r="K56" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57">
@@ -13878,7 +13878,7 @@
         <v>0.02221961152882206</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="n">
         <v>175993</v>
@@ -14174,7 +14174,7 @@
         <v>0.02221961152882206</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
         <v>175993</v>
@@ -16871,7 +16871,7 @@
         <v>0.09201228878648234</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -17130,7 +17130,7 @@
         <v>0.09201228878648234</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -19716,7 +19716,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -19975,7 +19975,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -22561,7 +22561,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -22820,7 +22820,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2993,7 +2993,7 @@
         <v>17263</v>
       </c>
       <c r="K56" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
@@ -6541,7 +6541,7 @@
         <v>18384</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -13637,7 +13637,7 @@
         <v>28637</v>
       </c>
       <c r="K56" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2993,7 +2993,7 @@
         <v>17263</v>
       </c>
       <c r="K56" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57">
@@ -6541,7 +6541,7 @@
         <v>18384</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
@@ -13637,7 +13637,7 @@
         <v>28637</v>
       </c>
       <c r="K56" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2993,7 +2993,7 @@
         <v>17263</v>
       </c>
       <c r="K56" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57">
@@ -6541,7 +6541,7 @@
         <v>18384</v>
       </c>
       <c r="K56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2993,7 +2993,7 @@
         <v>17263</v>
       </c>
       <c r="K56" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
@@ -6541,7 +6541,7 @@
         <v>18384</v>
       </c>
       <c r="K56" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
@@ -13634,10 +13634,10 @@
         <v>0.3321438920866171</v>
       </c>
       <c r="J56" t="n">
-        <v>28637</v>
+        <v>28635</v>
       </c>
       <c r="K56" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2990,10 +2990,10 @@
         <v>0.04090318004492257</v>
       </c>
       <c r="J56" t="n">
-        <v>17263</v>
+        <v>17301</v>
       </c>
       <c r="K56" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
@@ -6541,7 +6541,7 @@
         <v>18384</v>
       </c>
       <c r="K56" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
@@ -13637,7 +13637,7 @@
         <v>28635</v>
       </c>
       <c r="K56" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2990,10 +2990,10 @@
         <v>0.04090318004492257</v>
       </c>
       <c r="J56" t="n">
-        <v>17301</v>
+        <v>17302</v>
       </c>
       <c r="K56" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2975,7 +2975,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>51054</v>
@@ -2993,7 +2993,7 @@
         <v>17302</v>
       </c>
       <c r="K56" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57">
@@ -6523,25 +6523,25 @@
         <v>-0.01092144561784586</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>243237</v>
+        <v>196403</v>
       </c>
       <c r="G56" t="n">
-        <v>4444</v>
+        <v>50527</v>
       </c>
       <c r="H56" t="n">
-        <v>6053</v>
+        <v>6306</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.3720023575596014</v>
+        <v>0.3693095486571102</v>
       </c>
       <c r="J56" t="n">
         <v>18384</v>
       </c>
       <c r="K56" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.4638834369851892</v>
+        <v>-0.4628291396168001</v>
       </c>
       <c r="J57" t="n">
         <v>4167</v>
@@ -10071,7 +10071,7 @@
         <v>0.02477763659466328</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>36403</v>
@@ -10089,7 +10089,7 @@
         <v>4082</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -13619,7 +13619,7 @@
         <v>-0.0007355363669100577</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>231803</v>
@@ -13637,7 +13637,7 @@
         <v>28635</v>
       </c>
       <c r="K56" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57">
@@ -16686,7 +16686,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19531,7 +19531,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -22376,7 +22376,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2975,7 +2975,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>51054</v>
@@ -6523,7 +6523,7 @@
         <v>-0.01092144561784586</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>196403</v>
@@ -10071,7 +10071,7 @@
         <v>0.02477763659466328</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>36403</v>
@@ -13619,7 +13619,7 @@
         <v>-0.0007355363669100577</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>231803</v>
@@ -16686,7 +16686,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19531,7 +19531,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -22376,7 +22376,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -2975,7 +2975,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>51054</v>
@@ -2990,7 +2990,7 @@
         <v>0.04090318004492257</v>
       </c>
       <c r="J56" t="n">
-        <v>17302</v>
+        <v>17304</v>
       </c>
       <c r="K56" t="n">
         <v>57</v>
@@ -6523,7 +6523,7 @@
         <v>-0.01092144561784586</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>196403</v>
@@ -10071,7 +10071,7 @@
         <v>0.02477763659466328</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>36403</v>
@@ -13619,7 +13619,7 @@
         <v>-0.0007355363669100577</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>231803</v>
@@ -16686,7 +16686,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19531,7 +19531,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -22376,7 +22376,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3258,57 +3258,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/2019</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>152874</v>
+        <v>160472</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>3.115905450964996e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>12033</v>
+        <v>51054</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.762915238207826</v>
+        <v>0.04090318004492257</v>
       </c>
       <c r="J64" t="n">
-        <v>4773</v>
+        <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>6859</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>09/2019</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04734782391943766</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>12033</v>
@@ -3320,13 +3320,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0</v>
+        <v>-0.7722316865417377</v>
       </c>
       <c r="J65" t="n">
-        <v>4931</v>
+        <v>4773</v>
       </c>
       <c r="K65" t="n">
-        <v>7880</v>
+        <v>6859</v>
       </c>
     </row>
     <row r="66">
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E66" t="n">
         <v>4</v>
@@ -3369,7 +3369,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3382,10 +3382,10 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -3394,19 +3394,19 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>9584</v>
+        <v>4931</v>
       </c>
       <c r="K67" t="n">
-        <v>3870</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" t="n">
         <v>38207</v>
@@ -3431,29 +3431,29 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J68" t="n">
-        <v>13409</v>
+        <v>9584</v>
       </c>
       <c r="K68" t="n">
-        <v>672</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>153028</v>
+        <v>159858</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.04272541880919316</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>4</v>
@@ -3471,32 +3471,32 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>14940</v>
+        <v>13409</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>156726</v>
+        <v>153028</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.02416551219384688</v>
+        <v>-0.04272541880919316</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>51022</v>
+        <v>38207</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3505,35 +3505,35 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.3354097416703745</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>15205</v>
+        <v>14940</v>
       </c>
       <c r="K70" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>160467</v>
+        <v>156726</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.0238696833965009</v>
+        <v>0.02416551219384688</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>50774</v>
+        <v>51022</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -3542,35 +3542,35 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>-0.00486064834777155</v>
+        <v>0.3354097416703745</v>
       </c>
       <c r="J71" t="n">
-        <v>16576</v>
+        <v>15205</v>
       </c>
       <c r="K71" t="n">
-        <v>103</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>152874</v>
+        <v>160467</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>0.0238696833965009</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>12033</v>
+        <v>50774</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3579,35 +3579,35 @@
         <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>-0.7630086264623627</v>
+        <v>-0.00486064834777155</v>
       </c>
       <c r="J72" t="n">
-        <v>4773</v>
+        <v>16576</v>
       </c>
       <c r="K72" t="n">
-        <v>6859</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04731814017835443</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3616,13 +3616,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.7630086264623627</v>
       </c>
       <c r="J73" t="n">
-        <v>4730</v>
+        <v>4773</v>
       </c>
       <c r="K73" t="n">
-        <v>8111</v>
+        <v>6859</v>
       </c>
     </row>
     <row r="74">
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E74" t="n">
         <v>4</v>
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J74" t="n">
         <v>4730</v>
@@ -3665,7 +3665,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>38207</v>
@@ -3693,16 +3693,16 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>10235</v>
+        <v>4730</v>
       </c>
       <c r="K75" t="n">
-        <v>3318</v>
+        <v>8111</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>38207</v>
@@ -3730,29 +3730,29 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>13721</v>
+        <v>10235</v>
       </c>
       <c r="K76" t="n">
-        <v>361</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>153028</v>
+        <v>159858</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>-0.04272541880919316</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
         <v>38207</v>
@@ -3767,32 +3767,32 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>14567</v>
+        <v>13721</v>
       </c>
       <c r="K77" t="n">
-        <v>81</v>
+        <v>361</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>156726</v>
+        <v>153028</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.02416551219384688</v>
+        <v>-0.04272541880919316</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>51022</v>
+        <v>38207</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3801,35 +3801,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.3354097416703745</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>15253</v>
+        <v>14567</v>
       </c>
       <c r="K78" t="n">
-        <v>475</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>160467</v>
+        <v>156726</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.0238696833965009</v>
+        <v>0.02416551219384688</v>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>51392</v>
+        <v>51022</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3838,35 +3838,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.007251773744659166</v>
+        <v>0.3354097416703745</v>
       </c>
       <c r="J79" t="n">
-        <v>16702</v>
+        <v>15253</v>
       </c>
       <c r="K79" t="n">
-        <v>46</v>
+        <v>475</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>152874</v>
+        <v>160467</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>0.0238696833965009</v>
       </c>
       <c r="E80" t="n">
         <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>12033</v>
+        <v>51392</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3875,35 +3875,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-0.765858499377335</v>
+        <v>0.007251773744659166</v>
       </c>
       <c r="J80" t="n">
-        <v>3662</v>
+        <v>16702</v>
       </c>
       <c r="K80" t="n">
-        <v>8545</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04731814017835443</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3912,13 +3912,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.765858499377335</v>
       </c>
       <c r="J81" t="n">
-        <v>4730</v>
+        <v>3662</v>
       </c>
       <c r="K81" t="n">
-        <v>8150</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="82">
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J82" t="n">
         <v>4730</v>
@@ -3961,7 +3961,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>38207</v>
@@ -3989,16 +3989,16 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>10614</v>
+        <v>4730</v>
       </c>
       <c r="K83" t="n">
-        <v>2993</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
         <v>38207</v>
@@ -4026,29 +4026,29 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>13731</v>
+        <v>10614</v>
       </c>
       <c r="K84" t="n">
-        <v>448</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>153028</v>
+        <v>159858</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.04272541880919316</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F85" t="n">
         <v>38207</v>
@@ -4063,32 +4063,32 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>14569</v>
+        <v>13731</v>
       </c>
       <c r="K85" t="n">
-        <v>161</v>
+        <v>448</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>156789</v>
+        <v>153028</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.02457720155788483</v>
+        <v>-0.04272541880919316</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>50754</v>
+        <v>38207</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -4097,35 +4097,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.3283953202292774</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>15510</v>
+        <v>14569</v>
       </c>
       <c r="K86" t="n">
-        <v>298</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>160467</v>
+        <v>156789</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02345827832309665</v>
+        <v>0.02457720155788483</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>51392</v>
+        <v>50754</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4134,35 +4134,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.01257043779800607</v>
+        <v>0.3283953202292774</v>
       </c>
       <c r="J87" t="n">
-        <v>16702</v>
+        <v>15510</v>
       </c>
       <c r="K87" t="n">
-        <v>141</v>
+        <v>298</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>152874</v>
+        <v>160467</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>0.02345827832309665</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>12033</v>
+        <v>51392</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4171,35 +4171,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.765858499377335</v>
+        <v>0.01257043779800607</v>
       </c>
       <c r="J88" t="n">
-        <v>3662</v>
+        <v>16702</v>
       </c>
       <c r="K88" t="n">
-        <v>8545</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04731814017835443</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4208,19 +4208,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.765858499377335</v>
       </c>
       <c r="J89" t="n">
-        <v>4730</v>
+        <v>3662</v>
       </c>
       <c r="K89" t="n">
-        <v>8228</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4230,10 +4230,10 @@
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>38207</v>
@@ -4245,19 +4245,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J90" t="n">
-        <v>11517</v>
+        <v>4730</v>
       </c>
       <c r="K90" t="n">
-        <v>2170</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>38207</v>
@@ -4285,29 +4285,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>13931</v>
+        <v>11517</v>
       </c>
       <c r="K91" t="n">
-        <v>376</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>154830</v>
+        <v>159858</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.03145291446158466</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>38207</v>
@@ -4322,32 +4322,32 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>14569</v>
+        <v>13931</v>
       </c>
       <c r="K92" t="n">
-        <v>259</v>
+        <v>376</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>160191</v>
+        <v>154830</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.03462507266033715</v>
+        <v>-0.03145291446158466</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>50754</v>
+        <v>38207</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4356,71 +4356,108 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.3283953202292774</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>15886</v>
+        <v>14569</v>
       </c>
       <c r="K93" t="n">
-        <v>14</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>160467</v>
+        <v>160191</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.001722943236511414</v>
+        <v>0.03462507266033715</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
+        <v>50754</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.3283953202292774</v>
+      </c>
+      <c r="J94" t="n">
+        <v>15886</v>
+      </c>
+      <c r="K94" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>160467</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.001722943236511414</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
         <v>51427</v>
       </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
         <v>1776</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>0.04825235449422706</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J95" t="n">
         <v>16723</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K95" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B96" s="4" t="n">
         <v>7593</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>39394</v>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4" t="n">
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
         <v>1776</v>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J96" s="4" t="n">
         <v>13061</v>
       </c>
     </row>
@@ -4436,7 +4473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6806,60 +6843,60 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/2019</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>195596</v>
+        <v>276851</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.3013779850986163</v>
+        <v>-0.01115460721352697</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>150804</v>
+        <v>196403</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>50527</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>6306</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.2589848164709351</v>
+        <v>0.2443418013856813</v>
       </c>
       <c r="J64" t="n">
-        <v>4167</v>
+        <v>18384</v>
       </c>
       <c r="K64" t="n">
-        <v>7562</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>09/2019</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>186047</v>
+        <v>195596</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.04882001676925909</v>
+        <v>-0.2934972241386161</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>107276</v>
+        <v>150804</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -6868,13 +6905,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.288639558632397</v>
+        <v>-0.4044922522864048</v>
       </c>
       <c r="J65" t="n">
-        <v>3624</v>
+        <v>4167</v>
       </c>
       <c r="K65" t="n">
-        <v>9034</v>
+        <v>7562</v>
       </c>
     </row>
     <row r="66">
@@ -6890,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>-0.04882001676925909</v>
       </c>
       <c r="E66" t="n">
         <v>4</v>
@@ -6905,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>-0.288639558632397</v>
       </c>
       <c r="J66" t="n">
         <v>3624</v>
@@ -6917,23 +6954,23 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>201697</v>
+        <v>186047</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.08411852918886088</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>139905</v>
+        <v>107276</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -6942,35 +6979,35 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.3041593646295537</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>13477</v>
+        <v>3624</v>
       </c>
       <c r="K67" t="n">
-        <v>49</v>
+        <v>9034</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0.08411852918886088</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" t="n">
-        <v>158599</v>
+        <v>139905</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -6979,35 +7016,35 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1336192416282477</v>
+        <v>0.3041593646295537</v>
       </c>
       <c r="J68" t="n">
-        <v>14489</v>
+        <v>13477</v>
       </c>
       <c r="K68" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>264414</v>
+        <v>223030</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.1855535129803166</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E69" t="n">
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>200191</v>
+        <v>158599</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -7016,35 +7053,35 @@
         <v>0</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.2622462941128254</v>
+        <v>0.1336192416282477</v>
       </c>
       <c r="J69" t="n">
-        <v>15282</v>
+        <v>14489</v>
       </c>
       <c r="K69" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>280969</v>
+        <v>264414</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.06261014923566831</v>
+        <v>0.1855535129803166</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>208147</v>
+        <v>200191</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -7053,35 +7090,35 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.03974204634573982</v>
+        <v>0.2622462941128254</v>
       </c>
       <c r="J70" t="n">
-        <v>16150</v>
+        <v>15282</v>
       </c>
       <c r="K70" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>279974</v>
+        <v>280969</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>-0.003541315945887269</v>
+        <v>0.06261014923566831</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>206373</v>
+        <v>208147</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -7090,35 +7127,35 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>-0.0085228228127237</v>
+        <v>0.03974204634573982</v>
       </c>
       <c r="J71" t="n">
-        <v>17462</v>
+        <v>16150</v>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>195596</v>
+        <v>279974</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-0.3013779850986163</v>
+        <v>-0.003541315945887269</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>150804</v>
+        <v>206373</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -7127,35 +7164,35 @@
         <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>-0.2692648747655944</v>
+        <v>-0.0085228228127237</v>
       </c>
       <c r="J72" t="n">
-        <v>4167</v>
+        <v>17462</v>
       </c>
       <c r="K72" t="n">
-        <v>7562</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>186047</v>
+        <v>195596</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.04882001676925909</v>
+        <v>-0.3013779850986163</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>145022</v>
+        <v>150804</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -7164,13 +7201,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.03834115805946792</v>
+        <v>-0.2692648747655944</v>
       </c>
       <c r="J73" t="n">
-        <v>3624</v>
+        <v>4167</v>
       </c>
       <c r="K73" t="n">
-        <v>9077</v>
+        <v>7562</v>
       </c>
     </row>
     <row r="74">
@@ -7186,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>-0.04882001676925909</v>
       </c>
       <c r="E74" t="n">
         <v>4</v>
@@ -7201,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>-0.03834115805946792</v>
       </c>
       <c r="J74" t="n">
         <v>3624</v>
@@ -7213,23 +7250,23 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>201697</v>
+        <v>186047</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.08411852918886088</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>139905</v>
+        <v>145022</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -7238,35 +7275,35 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>-0.03528430169215705</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>13526</v>
+        <v>3624</v>
       </c>
       <c r="K75" t="n">
-        <v>52</v>
+        <v>9077</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0.08411852918886088</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>158599</v>
+        <v>139905</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -7275,35 +7312,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1336192416282477</v>
+        <v>-0.03528430169215705</v>
       </c>
       <c r="J76" t="n">
-        <v>14562</v>
+        <v>13526</v>
       </c>
       <c r="K76" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>264414</v>
+        <v>223030</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.1855535129803166</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
-        <v>200191</v>
+        <v>158599</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -7312,35 +7349,35 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.2622462941128254</v>
+        <v>0.1336192416282477</v>
       </c>
       <c r="J77" t="n">
-        <v>15164</v>
+        <v>14562</v>
       </c>
       <c r="K77" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>280969</v>
+        <v>264414</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.06261014923566831</v>
+        <v>0.1855535129803166</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>208147</v>
+        <v>200191</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -7349,35 +7386,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.03974204634573982</v>
+        <v>0.2622462941128254</v>
       </c>
       <c r="J78" t="n">
-        <v>16288</v>
+        <v>15164</v>
       </c>
       <c r="K78" t="n">
-        <v>25</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>279974</v>
+        <v>280969</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>-0.003541315945887269</v>
+        <v>0.06261014923566831</v>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>239255</v>
+        <v>208147</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -7386,35 +7423,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1494520699313466</v>
+        <v>0.03974204634573982</v>
       </c>
       <c r="J79" t="n">
-        <v>17585</v>
+        <v>16288</v>
       </c>
       <c r="K79" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>190349</v>
+        <v>279974</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.3201190110510262</v>
+        <v>-0.003541315945887269</v>
       </c>
       <c r="E80" t="n">
         <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>136031</v>
+        <v>239255</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -7423,35 +7460,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-0.4314392593676203</v>
+        <v>0.1494520699313466</v>
       </c>
       <c r="J80" t="n">
-        <v>3632</v>
+        <v>17585</v>
       </c>
       <c r="K80" t="n">
-        <v>8333</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>201697</v>
+        <v>190349</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.05961680912429275</v>
+        <v>-0.3201190110510262</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>137131</v>
+        <v>136031</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -7460,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.008086392072395263</v>
+        <v>-0.4314392593676203</v>
       </c>
       <c r="J81" t="n">
-        <v>4596</v>
+        <v>3632</v>
       </c>
       <c r="K81" t="n">
-        <v>8459</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="82">
@@ -7482,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>0.05961680912429275</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -7497,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>0.008086392072395263</v>
       </c>
       <c r="J82" t="n">
         <v>4596</v>
@@ -7509,7 +7546,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -7522,10 +7559,10 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>139905</v>
+        <v>137131</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7534,35 +7571,35 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.02022883228445793</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>13526</v>
+        <v>4596</v>
       </c>
       <c r="K83" t="n">
-        <v>139</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>158599</v>
+        <v>139905</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7571,35 +7608,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.1336192416282477</v>
+        <v>0.02022883228445793</v>
       </c>
       <c r="J84" t="n">
-        <v>14722</v>
+        <v>13526</v>
       </c>
       <c r="K84" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>264805</v>
+        <v>223030</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.1873066403622831</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E85" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F85" t="n">
-        <v>194280</v>
+        <v>158599</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7608,35 +7645,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.2249761978322688</v>
+        <v>0.1336192416282477</v>
       </c>
       <c r="J85" t="n">
-        <v>15357</v>
+        <v>14722</v>
       </c>
       <c r="K85" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>280921</v>
+        <v>264805</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.06085987802345122</v>
+        <v>0.1873066403622831</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>193280</v>
+        <v>194280</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7645,35 +7682,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.005147210212065061</v>
+        <v>0.2249761978322688</v>
       </c>
       <c r="J86" t="n">
-        <v>16288</v>
+        <v>15357</v>
       </c>
       <c r="K86" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>279057</v>
+        <v>280921</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.006635317402401386</v>
+        <v>0.06085987802345122</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>239263</v>
+        <v>193280</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7682,35 +7719,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.2379087334437086</v>
+        <v>-0.005147210212065061</v>
       </c>
       <c r="J87" t="n">
-        <v>17672</v>
+        <v>16288</v>
       </c>
       <c r="K87" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>190349</v>
+        <v>279057</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.3178848765664363</v>
+        <v>-0.006635317402401386</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>136031</v>
+        <v>239263</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -7719,35 +7756,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.4314582697700856</v>
+        <v>0.2379087334437086</v>
       </c>
       <c r="J88" t="n">
-        <v>3632</v>
+        <v>17672</v>
       </c>
       <c r="K88" t="n">
-        <v>8333</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>201697</v>
+        <v>190349</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.05961680912429275</v>
+        <v>-0.3178848765664363</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>137131</v>
+        <v>136031</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -7756,19 +7793,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.008086392072395263</v>
+        <v>-0.4314582697700856</v>
       </c>
       <c r="J89" t="n">
-        <v>5832</v>
+        <v>3632</v>
       </c>
       <c r="K89" t="n">
-        <v>7409</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -7778,13 +7815,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0</v>
+        <v>0.05961680912429275</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>140221</v>
+        <v>137131</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -7793,35 +7830,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.02253319818275955</v>
+        <v>0.008086392072395263</v>
       </c>
       <c r="J90" t="n">
-        <v>13526</v>
+        <v>5832</v>
       </c>
       <c r="K90" t="n">
-        <v>201</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>158599</v>
+        <v>140221</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -7830,35 +7867,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.131064533843005</v>
+        <v>0.02253319818275955</v>
       </c>
       <c r="J91" t="n">
-        <v>14777</v>
+        <v>13526</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>264838</v>
+        <v>223030</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.1874546025198404</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>194280</v>
+        <v>158599</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -7867,35 +7904,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.2249761978322688</v>
+        <v>0.131064533843005</v>
       </c>
       <c r="J92" t="n">
-        <v>15421</v>
+        <v>14777</v>
       </c>
       <c r="K92" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>282361</v>
+        <v>264838</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.06616497632514971</v>
+        <v>0.1874546025198404</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>193280</v>
+        <v>194280</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -7904,71 +7941,108 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>-0.005147210212065061</v>
+        <v>0.2249761978322688</v>
       </c>
       <c r="J93" t="n">
-        <v>16354</v>
+        <v>15421</v>
       </c>
       <c r="K93" t="n">
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>277864</v>
+        <v>282361</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.0159264204334168</v>
+        <v>0.06616497632514971</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
+        <v>193280</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>-0.005147210212065061</v>
+      </c>
+      <c r="J94" t="n">
+        <v>16354</v>
+      </c>
+      <c r="K94" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>277864</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>-0.0159264204334168</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
         <v>247810</v>
       </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
         <v>1193</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>0.2883019453642384</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J95" t="n">
         <v>17787</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K95" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B96" s="4" t="n">
         <v>88824</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>111779</v>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4" t="n">
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
         <v>1193</v>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J96" s="4" t="n">
         <v>14155</v>
       </c>
     </row>
@@ -7984,7 +8058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10354,44 +10428,44 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/2019</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>44862</v>
+        <v>50003</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.007089484602525629</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>36001</v>
+        <v>36403</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>18266</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>0.4830719982637947</v>
       </c>
       <c r="J64" t="n">
-        <v>659</v>
+        <v>4082</v>
       </c>
       <c r="K64" t="n">
-        <v>2065</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>09/2019</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -10401,10 +10475,10 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0</v>
+        <v>-0.1028138311701298</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>36001</v>
@@ -10416,13 +10490,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0</v>
+        <v>-0.341473229801167</v>
       </c>
       <c r="J65" t="n">
-        <v>230</v>
+        <v>659</v>
       </c>
       <c r="K65" t="n">
-        <v>2643</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="66">
@@ -10465,7 +10539,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -10478,10 +10552,10 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10490,19 +10564,19 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="K67" t="n">
-        <v>2720</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -10515,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" t="n">
         <v>8468</v>
@@ -10527,35 +10601,35 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J68" t="n">
-        <v>3007</v>
+        <v>223</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>46293</v>
+        <v>44862</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.03189781998127592</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>14963</v>
+        <v>8468</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -10564,35 +10638,35 @@
         <v>0</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.7670051960321209</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>3245</v>
+        <v>3007</v>
       </c>
       <c r="K69" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>-0.000216015380295077</v>
+        <v>0.03189781998127592</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>36656</v>
+        <v>14963</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -10601,35 +10675,35 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.449776114415558</v>
+        <v>0.7670051960321209</v>
       </c>
       <c r="J70" t="n">
-        <v>3747</v>
+        <v>3245</v>
       </c>
       <c r="K70" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>49651</v>
+        <v>46283</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.07276969945768424</v>
+        <v>-0.000216015380295077</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>36862</v>
+        <v>36656</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -10638,35 +10712,35 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.00561981667394151</v>
+        <v>1.449776114415558</v>
       </c>
       <c r="J71" t="n">
-        <v>3877</v>
+        <v>3747</v>
       </c>
       <c r="K71" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>44862</v>
+        <v>49651</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.07276969945768424</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>36001</v>
+        <v>36862</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -10675,19 +10749,19 @@
         <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>0.00561981667394151</v>
       </c>
       <c r="J72" t="n">
-        <v>659</v>
+        <v>3877</v>
       </c>
       <c r="K72" t="n">
-        <v>2065</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -10697,13 +10771,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>-0.09645324364061147</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -10712,13 +10786,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.02335738701101405</v>
       </c>
       <c r="J73" t="n">
-        <v>230</v>
+        <v>659</v>
       </c>
       <c r="K73" t="n">
-        <v>2660</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="74">
@@ -10749,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J74" t="n">
         <v>230</v>
@@ -10761,7 +10835,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -10774,7 +10848,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>8468</v>
@@ -10789,16 +10863,16 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>753</v>
+        <v>230</v>
       </c>
       <c r="K75" t="n">
-        <v>2199</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -10811,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>8468</v>
@@ -10826,32 +10900,32 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>3007</v>
+        <v>753</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>46293</v>
+        <v>44862</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.03189781998127592</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
-        <v>14963</v>
+        <v>8468</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -10860,35 +10934,35 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.7670051960321209</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>3244</v>
+        <v>3007</v>
       </c>
       <c r="K77" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-0.000216015380295077</v>
+        <v>0.03189781998127592</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>36656</v>
+        <v>14963</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -10897,35 +10971,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.449776114415558</v>
+        <v>0.7670051960321209</v>
       </c>
       <c r="J78" t="n">
-        <v>3774</v>
+        <v>3244</v>
       </c>
       <c r="K78" t="n">
-        <v>11</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>49651</v>
+        <v>46283</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.07276969945768424</v>
+        <v>-0.000216015380295077</v>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>36862</v>
+        <v>36656</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -10934,35 +11008,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.00561981667394151</v>
+        <v>1.449776114415558</v>
       </c>
       <c r="J79" t="n">
-        <v>3877</v>
+        <v>3774</v>
       </c>
       <c r="K79" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>44862</v>
+        <v>49651</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.07276969945768424</v>
       </c>
       <c r="E80" t="n">
         <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>36001</v>
+        <v>36862</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -10971,19 +11045,19 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>0.00561981667394151</v>
       </c>
       <c r="J80" t="n">
-        <v>230</v>
+        <v>3877</v>
       </c>
       <c r="K80" t="n">
-        <v>2574</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -10993,13 +11067,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0</v>
+        <v>-0.09645324364061147</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -11008,13 +11082,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.02335738701101405</v>
       </c>
       <c r="J81" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K81" t="n">
-        <v>2670</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="82">
@@ -11045,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J82" t="n">
         <v>225</v>
@@ -11057,7 +11131,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -11070,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>8468</v>
@@ -11085,32 +11159,32 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>2952</v>
+        <v>225</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>48086</v>
+        <v>44862</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.07186482992287459</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>11249</v>
+        <v>8468</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -11119,10 +11193,10 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.3284128483703354</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>3036</v>
+        <v>2952</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -11131,23 +11205,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>46293</v>
+        <v>48086</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.03728736014640436</v>
+        <v>0.07186482992287459</v>
       </c>
       <c r="E85" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F85" t="n">
-        <v>14963</v>
+        <v>11249</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11156,35 +11230,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.3301626811272113</v>
+        <v>0.3284128483703354</v>
       </c>
       <c r="J85" t="n">
-        <v>3403</v>
+        <v>3036</v>
       </c>
       <c r="K85" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.000216015380295077</v>
+        <v>-0.03728736014640436</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>50754</v>
+        <v>14963</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11193,35 +11267,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.391966851567199</v>
+        <v>0.3301626811272113</v>
       </c>
       <c r="J86" t="n">
-        <v>3774</v>
+        <v>3403</v>
       </c>
       <c r="K86" t="n">
-        <v>43</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>49651</v>
+        <v>46283</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.07276969945768424</v>
+        <v>-0.000216015380295077</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>36862</v>
+        <v>50754</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11230,35 +11304,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>-0.2737124167553296</v>
+        <v>2.391966851567199</v>
       </c>
       <c r="J87" t="n">
-        <v>3877</v>
+        <v>3774</v>
       </c>
       <c r="K87" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>44862</v>
+        <v>49651</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.07276969945768424</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>36001</v>
+        <v>36862</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11267,19 +11341,19 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>-0.2737124167553296</v>
       </c>
       <c r="J88" t="n">
-        <v>230</v>
+        <v>3877</v>
       </c>
       <c r="K88" t="n">
-        <v>2574</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -11289,13 +11363,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0</v>
+        <v>-0.09645324364061147</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11304,19 +11378,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.02335738701101405</v>
       </c>
       <c r="J89" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K89" t="n">
-        <v>2673</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -11329,7 +11403,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>8468</v>
@@ -11341,35 +11415,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J90" t="n">
-        <v>2952</v>
+        <v>225</v>
       </c>
       <c r="K90" t="n">
-        <v>8</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>48086</v>
+        <v>44862</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.07186482992287459</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>14963</v>
+        <v>8468</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11378,35 +11452,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.7670051960321209</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>3036</v>
+        <v>2952</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>46293</v>
+        <v>48086</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.03728736014640436</v>
+        <v>0.07186482992287459</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>19193</v>
+        <v>14963</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11415,35 +11489,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.2826973200561385</v>
+        <v>0.7670051960321209</v>
       </c>
       <c r="J92" t="n">
-        <v>3403</v>
+        <v>3036</v>
       </c>
       <c r="K92" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>46924</v>
+        <v>46293</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01363057049661936</v>
+        <v>-0.03728736014640436</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>50754</v>
+        <v>19193</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11452,71 +11526,108 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>1.644401604751732</v>
+        <v>0.2826973200561385</v>
       </c>
       <c r="J93" t="n">
-        <v>3774</v>
+        <v>3403</v>
       </c>
       <c r="K93" t="n">
-        <v>68</v>
+        <v>262</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>49651</v>
+        <v>46924</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.05811525019179951</v>
+        <v>0.01363057049661936</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
+        <v>50754</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>1.644401604751732</v>
+      </c>
+      <c r="J94" t="n">
+        <v>3774</v>
+      </c>
+      <c r="K94" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>49651</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.05811525019179951</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
         <v>36628</v>
       </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
         <v>17602</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>0.06848721283051581</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J95" t="n">
         <v>3928</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K95" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B96" s="4" t="n">
         <v>4789</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>627</v>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4" t="n">
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
         <v>17602</v>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J96" s="4" t="n">
         <v>3698</v>
       </c>
     </row>
@@ -11532,7 +11643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13902,60 +14013,60 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/2019</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>240624</v>
+        <v>260842</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.0781890481699702</v>
+        <v>-0.0007355363669100577</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>42233</v>
+        <v>231803</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2645</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.7600302284749961</v>
+        <v>0.3321438920866171</v>
       </c>
       <c r="J64" t="n">
-        <v>12553</v>
+        <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>10373</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>09/2019</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>241854</v>
+        <v>240624</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.005111709555156592</v>
+        <v>-0.07751052361199499</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>77270</v>
+        <v>42233</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -13964,13 +14075,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.8296119148533138</v>
+        <v>-0.8198619736572715</v>
       </c>
       <c r="J65" t="n">
-        <v>8096</v>
+        <v>12553</v>
       </c>
       <c r="K65" t="n">
-        <v>17180</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="66">
@@ -13986,7 +14097,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>0.005111709555156592</v>
       </c>
       <c r="E66" t="n">
         <v>4</v>
@@ -14001,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>0.8296119148533138</v>
       </c>
       <c r="J66" t="n">
         <v>8096</v>
@@ -14013,23 +14124,23 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>243430</v>
+        <v>241854</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.006516328032614718</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>203597</v>
+        <v>77270</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -14038,35 +14149,35 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>1.634877701565938</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>25934</v>
+        <v>8096</v>
       </c>
       <c r="K67" t="n">
-        <v>290</v>
+        <v>17180</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>244292</v>
+        <v>243430</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.003541059031343713</v>
+        <v>0.006516328032614718</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" t="n">
-        <v>194558</v>
+        <v>203597</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -14075,35 +14186,35 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>-0.04439652843607715</v>
+        <v>1.634877701565938</v>
       </c>
       <c r="J68" t="n">
-        <v>25809</v>
+        <v>25934</v>
       </c>
       <c r="K68" t="n">
-        <v>496</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>245427</v>
+        <v>244292</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.004646079282170517</v>
+        <v>0.003541059031343713</v>
       </c>
       <c r="E69" t="n">
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -14112,35 +14223,35 @@
         <v>0</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.04439652843607715</v>
       </c>
       <c r="J69" t="n">
-        <v>26881</v>
+        <v>25809</v>
       </c>
       <c r="K69" t="n">
-        <v>198</v>
+        <v>496</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>255360</v>
+        <v>245427</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.04047231967142979</v>
+        <v>0.004646079282170517</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>194623</v>
+        <v>194753</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -14149,35 +14260,35 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>-0.0006675121820973233</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J70" t="n">
-        <v>27438</v>
+        <v>26881</v>
       </c>
       <c r="K70" t="n">
-        <v>82</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>261034</v>
+        <v>255360</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.02221961152882206</v>
+        <v>0.04047231967142979</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>175993</v>
+        <v>194623</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -14186,35 +14297,35 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>-0.09572352702404135</v>
+        <v>-0.0006675121820973233</v>
       </c>
       <c r="J71" t="n">
-        <v>27924</v>
+        <v>27438</v>
       </c>
       <c r="K71" t="n">
-        <v>304</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>240624</v>
+        <v>261034</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-0.0781890481699702</v>
+        <v>0.02221961152882206</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>42233</v>
+        <v>175993</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -14223,35 +14334,35 @@
         <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>-0.7600302284749961</v>
+        <v>-0.09572352702404135</v>
       </c>
       <c r="J72" t="n">
-        <v>12553</v>
+        <v>27924</v>
       </c>
       <c r="K72" t="n">
-        <v>10373</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>243285</v>
+        <v>240624</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01105874725713146</v>
+        <v>-0.0781890481699702</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>162649</v>
+        <v>42233</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -14260,13 +14371,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>2.851230080742547</v>
+        <v>-0.7600302284749961</v>
       </c>
       <c r="J73" t="n">
-        <v>8096</v>
+        <v>12553</v>
       </c>
       <c r="K73" t="n">
-        <v>17287</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="74">
@@ -14282,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>0.01105874725713146</v>
       </c>
       <c r="E74" t="n">
         <v>4</v>
@@ -14297,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>2.851230080742547</v>
       </c>
       <c r="J74" t="n">
         <v>8096</v>
@@ -14309,23 +14420,23 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>243430</v>
+        <v>243285</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.0005960087962677518</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>203597</v>
+        <v>162649</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -14334,35 +14445,35 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.2517568506415656</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>25933</v>
+        <v>8096</v>
       </c>
       <c r="K75" t="n">
-        <v>325</v>
+        <v>17287</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>244292</v>
+        <v>243430</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.003541059031343713</v>
+        <v>0.0005960087962677518</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>194558</v>
+        <v>203597</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -14371,35 +14482,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>-0.04439652843607715</v>
+        <v>0.2517568506415656</v>
       </c>
       <c r="J76" t="n">
-        <v>26195</v>
+        <v>25933</v>
       </c>
       <c r="K76" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>245427</v>
+        <v>244292</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.004646079282170517</v>
+        <v>0.003541059031343713</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -14408,35 +14519,35 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.04439652843607715</v>
       </c>
       <c r="J77" t="n">
-        <v>26640</v>
+        <v>26195</v>
       </c>
       <c r="K77" t="n">
-        <v>246</v>
+        <v>322</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>255354</v>
+        <v>245427</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.04044787248346759</v>
+        <v>0.004646079282170517</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -14445,35 +14556,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J78" t="n">
-        <v>27559</v>
+        <v>26640</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>263205</v>
+        <v>255354</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.03074555323198383</v>
+        <v>0.04044787248346759</v>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>239305</v>
+        <v>194288</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -14482,35 +14593,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.2317024211479865</v>
+        <v>-0.002387639728271195</v>
       </c>
       <c r="J79" t="n">
-        <v>27923</v>
+        <v>27559</v>
       </c>
       <c r="K79" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>242066</v>
+        <v>263205</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.08031382382553523</v>
+        <v>0.03074555323198383</v>
       </c>
       <c r="E80" t="n">
         <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>42233</v>
+        <v>239305</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -14519,35 +14630,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-0.8235181045109797</v>
+        <v>0.2317024211479865</v>
       </c>
       <c r="J80" t="n">
-        <v>8264</v>
+        <v>27923</v>
       </c>
       <c r="K80" t="n">
-        <v>17043</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>243285</v>
+        <v>242066</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.005035816678096056</v>
+        <v>-0.08031382382553523</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>192466</v>
+        <v>42233</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -14556,13 +14667,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>3.557241967182061</v>
+        <v>-0.8235181045109797</v>
       </c>
       <c r="J81" t="n">
-        <v>8093</v>
+        <v>8264</v>
       </c>
       <c r="K81" t="n">
-        <v>17836</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="82">
@@ -14578,7 +14689,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>0.005035816678096056</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -14593,7 +14704,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>3.557241967182061</v>
       </c>
       <c r="J82" t="n">
         <v>8093</v>
@@ -14605,23 +14716,23 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>243430</v>
+        <v>243285</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.0005960087962677518</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>195134</v>
+        <v>192466</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -14630,35 +14741,35 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.01386218864630636</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>25930</v>
+        <v>8093</v>
       </c>
       <c r="K83" t="n">
-        <v>369</v>
+        <v>17836</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>244292</v>
+        <v>243430</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.003541059031343713</v>
+        <v>0.0005960087962677518</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>194558</v>
+        <v>195134</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -14667,35 +14778,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>-0.002951817725255465</v>
+        <v>0.01386218864630636</v>
       </c>
       <c r="J84" t="n">
-        <v>26319</v>
+        <v>25930</v>
       </c>
       <c r="K84" t="n">
-        <v>200</v>
+        <v>369</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>245427</v>
+        <v>244292</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.004646079282170517</v>
+        <v>0.003541059031343713</v>
       </c>
       <c r="E85" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F85" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -14704,35 +14815,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.002951817725255465</v>
       </c>
       <c r="J85" t="n">
-        <v>26640</v>
+        <v>26319</v>
       </c>
       <c r="K85" t="n">
-        <v>287</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>255354</v>
+        <v>245427</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.04044787248346759</v>
+        <v>0.004646079282170517</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -14741,35 +14852,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J86" t="n">
-        <v>27559</v>
+        <v>26640</v>
       </c>
       <c r="K86" t="n">
-        <v>51</v>
+        <v>287</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>260851</v>
+        <v>255354</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02152697823413771</v>
+        <v>0.04044787248346759</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>236724</v>
+        <v>194288</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -14778,35 +14889,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.2184180186115458</v>
+        <v>-0.002387639728271195</v>
       </c>
       <c r="J87" t="n">
-        <v>27923</v>
+        <v>27559</v>
       </c>
       <c r="K87" t="n">
-        <v>454</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>242066</v>
+        <v>260851</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.07201429168375816</v>
+        <v>0.02152697823413771</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>42233</v>
+        <v>236724</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -14815,35 +14926,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.82159392372552</v>
+        <v>0.2184180186115458</v>
       </c>
       <c r="J88" t="n">
-        <v>8264</v>
+        <v>27923</v>
       </c>
       <c r="K88" t="n">
-        <v>17043</v>
+        <v>454</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>243285</v>
+        <v>242066</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.005035816678096056</v>
+        <v>-0.07201429168375816</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>192466</v>
+        <v>42233</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -14852,35 +14963,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>3.557241967182061</v>
+        <v>-0.82159392372552</v>
       </c>
       <c r="J89" t="n">
-        <v>8092</v>
+        <v>8264</v>
       </c>
       <c r="K89" t="n">
-        <v>17874</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>243440</v>
+        <v>243285</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.0006371128511827691</v>
+        <v>0.005035816678096056</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>195134</v>
+        <v>192466</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -14889,35 +15000,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.01386218864630636</v>
+        <v>3.557241967182061</v>
       </c>
       <c r="J90" t="n">
-        <v>25929</v>
+        <v>8092</v>
       </c>
       <c r="K90" t="n">
-        <v>399</v>
+        <v>17874</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>250208</v>
+        <v>243440</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02780151166611896</v>
+        <v>0.0006371128511827691</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>194558</v>
+        <v>195134</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -14926,35 +15037,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.002951817725255465</v>
+        <v>0.01386218864630636</v>
       </c>
       <c r="J91" t="n">
-        <v>26584</v>
+        <v>25929</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>245427</v>
+        <v>250208</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.01910810205908684</v>
+        <v>0.02780151166611896</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -14963,35 +15074,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.002951817725255465</v>
       </c>
       <c r="J92" t="n">
-        <v>26898</v>
+        <v>26584</v>
       </c>
       <c r="K92" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>258366</v>
+        <v>245427</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.05272036084049432</v>
+        <v>-0.01910810205908684</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -15000,71 +15111,108 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J93" t="n">
-        <v>27560</v>
+        <v>26898</v>
       </c>
       <c r="K93" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>260851</v>
+        <v>258366</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.009618138609569371</v>
+        <v>0.05272036084049432</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
+        <v>194288</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>-0.002387639728271195</v>
+      </c>
+      <c r="J94" t="n">
+        <v>27560</v>
+      </c>
+      <c r="K94" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>260851</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.009618138609569371</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
         <v>234378</v>
       </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
         <v>2645</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>0.2199569710944577</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J95" t="n">
         <v>28255</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K95" t="n">
         <v>181</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B96" s="4" t="n">
         <v>18785</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>192145</v>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4" t="n">
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
         <v>2645</v>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J96" s="4" t="n">
         <v>19991</v>
       </c>
     </row>
@@ -15080,7 +15228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -16895,20 +17043,20 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -16923,10 +17071,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -16942,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E50" t="n">
         <v>4</v>
@@ -16969,7 +17117,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -16982,7 +17130,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -17006,7 +17154,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -17019,7 +17167,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -17043,7 +17191,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -17071,20 +17219,20 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K53" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6510</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -17093,7 +17241,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -17108,29 +17256,29 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>30</v>
+        <v>364</v>
       </c>
       <c r="K54" t="n">
-        <v>355</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7109</v>
+        <v>6510</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.09201228878648234</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -17145,29 +17293,29 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>386</v>
+        <v>30</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>355</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-1</v>
+        <v>0.09201228878648234</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17182,10 +17330,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -17201,7 +17349,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -17228,7 +17376,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -17241,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -17265,7 +17413,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -17278,7 +17426,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -17302,7 +17450,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -17315,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -17330,20 +17478,20 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K60" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6707</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -17352,7 +17500,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -17367,29 +17515,29 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7109</v>
+        <v>6707</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.05993737885790965</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -17407,26 +17555,26 @@
         <v>386</v>
       </c>
       <c r="K62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>-1</v>
+        <v>0.05993737885790965</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -17441,10 +17589,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -17460,7 +17608,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -17487,7 +17635,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -17500,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -17518,13 +17666,13 @@
         <v>365</v>
       </c>
       <c r="K65" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -17537,7 +17685,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -17561,11 +17709,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6588</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -17574,7 +17722,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -17589,29 +17737,29 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K67" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6707</v>
+        <v>6588</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.01806314511232544</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -17626,29 +17774,29 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7109</v>
+        <v>6707</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.05993737885790965</v>
+        <v>0.01806314511232544</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -17666,26 +17814,26 @@
         <v>386</v>
       </c>
       <c r="K69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>-1</v>
+        <v>0.05993737885790965</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -17700,16 +17848,16 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -17719,10 +17867,10 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -17746,7 +17894,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -17759,7 +17907,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17783,11 +17931,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6588</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -17796,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -17811,29 +17959,29 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="K73" t="n">
-        <v>352</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>7109</v>
+        <v>6588</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.07908318154219794</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -17848,16 +17996,16 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>386</v>
+        <v>30</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -17867,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.07908318154219794</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -17888,28 +18036,65 @@
         <v>386</v>
       </c>
       <c r="K75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>7109</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>386</v>
+      </c>
+      <c r="K76" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B77" s="4" t="n">
         <v>7109</v>
       </c>
-      <c r="F76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="n">
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -17925,7 +18110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -19740,7 +19925,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -19753,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -19814,7 +19999,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -19827,7 +20012,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -19851,7 +20036,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -19864,7 +20049,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -19888,7 +20073,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -19925,7 +20110,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -19938,7 +20123,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -19962,7 +20147,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -19975,7 +20160,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -19999,7 +20184,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -20012,7 +20197,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20073,7 +20258,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -20086,7 +20271,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -20110,7 +20295,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -20123,7 +20308,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -20147,7 +20332,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -20160,7 +20345,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -20184,7 +20369,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -20197,7 +20382,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -20221,7 +20406,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -20234,7 +20419,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -20258,7 +20443,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -20271,7 +20456,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -20289,7 +20474,7 @@
         <v>185</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
@@ -20332,7 +20517,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -20345,7 +20530,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20363,13 +20548,13 @@
         <v>185</v>
       </c>
       <c r="K65" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -20382,7 +20567,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -20406,7 +20591,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -20419,7 +20604,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -20443,7 +20628,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -20456,7 +20641,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -20480,7 +20665,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -20493,7 +20678,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -20517,7 +20702,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -20530,7 +20715,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -20554,7 +20739,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -20567,7 +20752,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -20591,7 +20776,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -20604,7 +20789,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -20628,7 +20813,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -20641,7 +20826,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -20665,7 +20850,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -20678,7 +20863,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -20702,7 +20887,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -20737,24 +20922,61 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>185</v>
+      </c>
+      <c r="K76" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="n">
+      <c r="B77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20770,7 +20992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -22585,7 +22807,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -22598,7 +22820,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -22659,7 +22881,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -22672,7 +22894,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -22696,7 +22918,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -22709,7 +22931,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -22733,7 +22955,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -22770,7 +22992,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -22783,7 +23005,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -22807,7 +23029,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -22820,7 +23042,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -22844,7 +23066,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -22857,7 +23079,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22918,7 +23140,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -22931,7 +23153,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -22955,7 +23177,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -22968,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -22992,7 +23214,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -23005,7 +23227,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -23029,7 +23251,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -23042,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -23066,7 +23288,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -23079,7 +23301,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -23103,7 +23325,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -23116,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23134,7 +23356,7 @@
         <v>119</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -23177,7 +23399,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -23190,7 +23412,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23208,13 +23430,13 @@
         <v>119</v>
       </c>
       <c r="K65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -23227,7 +23449,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -23251,7 +23473,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -23264,7 +23486,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -23288,7 +23510,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -23301,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -23325,7 +23547,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -23338,7 +23560,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -23362,7 +23584,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -23375,7 +23597,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -23399,7 +23621,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -23412,7 +23634,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -23436,7 +23658,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -23449,7 +23671,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -23473,7 +23695,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -23486,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -23510,7 +23732,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -23523,7 +23745,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -23547,7 +23769,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -23582,24 +23804,61 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>119</v>
+      </c>
+      <c r="K76" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="n">
+      <c r="B77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3271,7 +3271,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>51054</v>
@@ -6856,7 +6856,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>196403</v>
@@ -10441,7 +10441,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>36403</v>
@@ -14026,7 +14026,7 @@
         <v>-0.0007355363669100577</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>231803</v>
@@ -17056,7 +17056,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -19938,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -22820,7 +22820,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3289,7 +3289,7 @@
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18384</v>
       </c>
       <c r="K64" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3289,7 +3289,7 @@
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18384</v>
       </c>
       <c r="K64" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3289,7 +3289,7 @@
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18384</v>
       </c>
       <c r="K64" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3271,7 +3271,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>51054</v>
@@ -3289,7 +3289,7 @@
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>75</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65">
@@ -6856,7 +6856,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>196403</v>
@@ -6871,10 +6871,10 @@
         <v>0.2443418013856813</v>
       </c>
       <c r="J64" t="n">
-        <v>18384</v>
+        <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>106</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -10441,7 +10441,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>36403</v>
@@ -10459,7 +10459,7 @@
         <v>4082</v>
       </c>
       <c r="K64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
@@ -14026,7 +14026,7 @@
         <v>-0.0007355363669100577</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>231803</v>
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>142</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65">
@@ -17056,7 +17056,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -19938,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -22820,7 +22820,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3289,7 +3289,7 @@
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3289,7 +3289,7 @@
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3274,22 +3274,22 @@
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>51054</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1776</v>
+        <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.04090318004492257</v>
+        <v>-1</v>
       </c>
       <c r="J64" t="n">
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65">
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.7722316865417377</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>4773</v>
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -10456,10 +10456,10 @@
         <v>0.4830719982637947</v>
       </c>
       <c r="J64" t="n">
-        <v>4082</v>
+        <v>4100</v>
       </c>
       <c r="K64" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3289,7 +3289,7 @@
         <v>17304</v>
       </c>
       <c r="K64" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65">
@@ -10459,7 +10459,7 @@
         <v>4100</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3234,7 +3234,7 @@
         <v>0.0238696833965009</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>50754</v>
@@ -3274,22 +3274,22 @@
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>50052</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-1</v>
+        <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17304</v>
+        <v>17288</v>
       </c>
       <c r="K64" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65">
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0</v>
+        <v>-0.7678282009724473</v>
       </c>
       <c r="J65" t="n">
         <v>4773</v>
@@ -3567,7 +3567,7 @@
         <v>0.0238696833965009</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>50774</v>
@@ -6819,7 +6819,7 @@
         <v>0.0460764752916209</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>203510</v>
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -7152,7 +7152,7 @@
         <v>-0.003541315945887269</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>206373</v>
@@ -10404,7 +10404,7 @@
         <v>0.07276969945768424</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>36862</v>
@@ -10459,7 +10459,7 @@
         <v>4100</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -10737,7 +10737,7 @@
         <v>0.07276969945768424</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>36862</v>
@@ -13989,7 +13989,7 @@
         <v>0.02221961152882206</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>175993</v>
@@ -14029,7 +14029,7 @@
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>231803</v>
+        <v>231867</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -14038,13 +14038,13 @@
         <v>2645</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.3321438920866171</v>
+        <v>0.3325075429136386</v>
       </c>
       <c r="J64" t="n">
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65">
@@ -14075,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.8198619736572715</v>
+        <v>-0.8199111346114485</v>
       </c>
       <c r="J65" t="n">
         <v>12553</v>
@@ -14322,7 +14322,7 @@
         <v>0.02221961152882206</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>175993</v>
@@ -17019,7 +17019,7 @@
         <v>0.09201228878648234</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -17315,7 +17315,7 @@
         <v>0.09201228878648234</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -20197,7 +20197,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22783,7 +22783,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3271,7 +3271,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>50052</v>
@@ -3286,10 +3286,10 @@
         <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17288</v>
+        <v>17329</v>
       </c>
       <c r="K64" t="n">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65">
@@ -6856,7 +6856,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>196403</v>
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65">
@@ -10441,7 +10441,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>36403</v>
@@ -10459,7 +10459,7 @@
         <v>4100</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
@@ -14026,7 +14026,7 @@
         <v>-0.0007355363669100577</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>231867</v>
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65">
@@ -17056,7 +17056,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -19938,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -22820,7 +22820,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3286,10 +3286,10 @@
         <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17329</v>
+        <v>17390</v>
       </c>
       <c r="K64" t="n">
-        <v>167</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65">
